--- a/brain/library/internal/scorecard/Fertility IVF Clinic Software Scorecard April 2026.xlsx
+++ b/brain/library/internal/scorecard/Fertility IVF Clinic Software Scorecard April 2026.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INITIAL SCREEN" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEMPLATE" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industry Scorecard" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_bdm.8018492968a5442495f20d90ab0edcf5.edm" hidden="1">#REF!</definedName>
@@ -837,7 +837,7 @@
     <row r="3">
       <c r="B3" s="61" t="inlineStr">
         <is>
-          <t>XX Initial Screen</t>
+          <t>Fertility / IVF Clinic Software — Initial Screen</t>
         </is>
       </c>
     </row>
@@ -869,13 +869,21 @@
           <t>Margins</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>15%+ EBITDA margins required</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Vertical SaaS EHR/PM; mature players operate at 20-30% EBITDA at scale (eIVF, IDEAS, BabySentry)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -883,13 +891,21 @@
           <t>Recurring Revenue</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Existing recurring/contractual revenue or clear path to convert</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>SaaS subscription model standard; per-clinic or per-cycle contracts, multi-year</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -897,13 +913,21 @@
           <t>Industry Growth</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Growth rate above GDP (~3%+)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>US fertility services ~8-10% CAGR (delayed childbearing, employer benefits, LGBTQ+ family building); software segment growing faster as clinics digitize</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -911,13 +935,21 @@
           <t>Growth TAM</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>$500M+ total addressable market (investor floor)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>~500 US fertility clinics x ~$75-150K ACV = ~$40-75M core SaaS TAM. Even including adjacencies (embryology lab software, cryo mgmt, donor/genetic, RCM, patient engagement), realistic US software TAM ~$200-400M. BELOW $500M investor floor.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="B11" s="62" t="inlineStr">
@@ -925,10 +957,19 @@
           <t>VERDICT</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>All 4 must pass to proceed to Industry Scorecard</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Growth TAM gate fails. Market is small &amp; concentrating (PE clinic rollups + Progyny/Maven vertical integration). Attractive economics but insufficient scale for G&amp;B.</t>
         </is>
       </c>
     </row>
@@ -945,10 +986,19 @@
           <t>Number of independently owned acquisition candidates</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>~10-15 vendors</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>Determines sprint duration, not go/no-go</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>eIVF (most installed), IDEAS, BabySentry, Artisan, ARTsync, Dossier, LifeFiles, EngagedMD, Embie, TMRW Life Sciences (cryo), Alife (AI). Independent owned: ~5-7.</t>
         </is>
       </c>
     </row>
@@ -958,10 +1008,19 @@
           <t>Sprint duration estimate</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>very fast</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>50+ = long sprint | 20-50 = focused | 10-20 = fast | &lt;10 = very fast</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>If pursued despite TAM fail, &lt;10 independent targets = very fast sprint</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1066,7 @@
     <row r="3" customFormat="1" s="28">
       <c r="B3" s="33" t="inlineStr">
         <is>
-          <t>XX Industry Scorecard</t>
+          <t>Fertility / IVF Clinic Software — Industry Scorecard</t>
         </is>
       </c>
       <c r="C3" s="30" t="n"/>
@@ -1028,7 +1087,7 @@
     <row r="5" ht="14.5" customHeight="1">
       <c r="B5" s="35" t="inlineStr">
         <is>
-          <t>XX  Industry Scorecard</t>
+          <t>Fertility / IVF Clinic Software — Industry Scorecard</t>
         </is>
       </c>
       <c r="C5" s="36" t="inlineStr">
@@ -1131,13 +1190,12 @@
         </is>
       </c>
       <c r="C9" s="50" t="n"/>
-      <c r="D9" s="56">
-        <f t="array" ref="D9">_xlfn.SWITCH(E9,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D9" s="56" t="n">
+        <v>2</v>
       </c>
       <c r="E9" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F9" s="9" t="n"/>
@@ -1158,7 +1216,7 @@
       </c>
       <c r="J9" s="23" t="inlineStr">
         <is>
-          <t>&gt;10% industry growth</t>
+          <t>US fertility services ~8-10% CAGR; software layer growing faster</t>
         </is>
       </c>
     </row>
@@ -1169,9 +1227,8 @@
         </is>
       </c>
       <c r="C10" s="50" t="n"/>
-      <c r="D10" s="56">
-        <f t="array" ref="D10">_xlfn.SWITCH(E10,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D10" s="56" t="n">
+        <v>3</v>
       </c>
       <c r="E10" s="48" t="inlineStr">
         <is>
@@ -1200,7 +1257,7 @@
       </c>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t>Data 'manipulation' is a huge pain point</t>
+          <t>Low digital penetration; clinics replatform ~once a decade, current cycle active</t>
         </is>
       </c>
     </row>
@@ -1211,9 +1268,8 @@
         </is>
       </c>
       <c r="C11" s="50" t="n"/>
-      <c r="D11" s="56">
-        <f t="array" ref="D11">_xlfn.SWITCH(E11,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D11" s="56" t="n">
+        <v>3</v>
       </c>
       <c r="E11" s="48" t="inlineStr">
         <is>
@@ -1236,7 +1292,11 @@
           <t>Mostly Headwinds</t>
         </is>
       </c>
-      <c r="J11" s="23" t="n"/>
+      <c r="J11" s="23" t="inlineStr">
+        <is>
+          <t>Tailwinds: delayed childbearing, employer fertility benefits (Progyny/Maven), LGBTQ+ family building, PE clinic consolidation</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
       <c r="B12" s="19" t="inlineStr">
@@ -1245,13 +1305,12 @@
         </is>
       </c>
       <c r="C12" s="51" t="n"/>
-      <c r="D12" s="57">
-        <f t="array" ref="D12">_xlfn.SWITCH(E12,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D12" s="57" t="n">
+        <v>3</v>
       </c>
       <c r="E12" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F12" s="21" t="n"/>
@@ -1272,7 +1331,7 @@
       </c>
       <c r="J12" s="24" t="inlineStr">
         <is>
-          <t>Data 'manipulation' is a huge pain point</t>
+          <t>Replatform cycle + PE-backed clinic groups standardizing tech stacks = strong catalyst</t>
         </is>
       </c>
     </row>
@@ -1301,9 +1360,8 @@
         </is>
       </c>
       <c r="C14" s="50" t="n"/>
-      <c r="D14" s="56">
-        <f t="array" ref="D14">_xlfn.SWITCH(E14,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D14" s="56" t="n">
+        <v>1</v>
       </c>
       <c r="E14" s="48" t="inlineStr">
         <is>
@@ -1328,7 +1386,7 @@
       </c>
       <c r="J14" s="23" t="inlineStr">
         <is>
-          <t>~7 well-known players</t>
+          <t>~10-15 software vendors — dozens level, not thousands</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1397,12 @@
         </is>
       </c>
       <c r="C15" s="51" t="n"/>
-      <c r="D15" s="57">
-        <f t="array" ref="D15">_xlfn.SWITCH(E15,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D15" s="57" t="n">
+        <v>1</v>
       </c>
       <c r="E15" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F15" s="21" t="n"/>
@@ -1366,7 +1423,7 @@
       </c>
       <c r="J15" s="24" t="inlineStr">
         <is>
-          <t>Largest has ~35% of market</t>
+          <t>Top 2-3 (eIVF, IDEAS, BabySentry) hold majority share; winner-take-most dynamics</t>
         </is>
       </c>
     </row>
@@ -1395,9 +1452,8 @@
         </is>
       </c>
       <c r="C17" s="50" t="n"/>
-      <c r="D17" s="56">
-        <f t="array" ref="D17">_xlfn.SWITCH(E17,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D17" s="56" t="n">
+        <v>3</v>
       </c>
       <c r="E17" s="48" t="inlineStr">
         <is>
@@ -1422,7 +1478,7 @@
       </c>
       <c r="J17" s="23" t="inlineStr">
         <is>
-          <t>~80%/~55% recurring/non-rec gross margin</t>
+          <t>SaaS gross margins 70-80% typical</t>
         </is>
       </c>
     </row>
@@ -1433,13 +1489,12 @@
         </is>
       </c>
       <c r="C18" s="50" t="n"/>
-      <c r="D18" s="56">
-        <f t="array" ref="D18">_xlfn.SWITCH(E18,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D18" s="56" t="n">
+        <v>2</v>
       </c>
       <c r="E18" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F18" s="9" t="n"/>
@@ -1460,7 +1515,7 @@
       </c>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t>Probably close to 30%</t>
+          <t>20-30% EBITDA at scale; lower sub-scale</t>
         </is>
       </c>
     </row>
@@ -1471,9 +1526,8 @@
         </is>
       </c>
       <c r="C19" s="51" t="n"/>
-      <c r="D19" s="57">
-        <f t="array" ref="D19">_xlfn.SWITCH(E19,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D19" s="57" t="n">
+        <v>3</v>
       </c>
       <c r="E19" s="48" t="inlineStr">
         <is>
@@ -1498,7 +1552,7 @@
       </c>
       <c r="J19" s="24" t="inlineStr">
         <is>
-          <t>Probably close to 20%</t>
+          <t>High ROTC — SaaS asset-light</t>
         </is>
       </c>
     </row>
@@ -1527,9 +1581,8 @@
         </is>
       </c>
       <c r="C21" s="50" t="n"/>
-      <c r="D21" s="56">
-        <f t="array" ref="D21">_xlfn.SWITCH(E21,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D21" s="56" t="n">
+        <v>3</v>
       </c>
       <c r="E21" s="48" t="inlineStr">
         <is>
@@ -1554,7 +1607,7 @@
       </c>
       <c r="J21" s="23" t="inlineStr">
         <is>
-          <t>Outstanding customer feedback</t>
+          <t>SART reporting, cryo chain-of-custody, embryology lab workflow = non-negotiable</t>
         </is>
       </c>
     </row>
@@ -1565,13 +1618,12 @@
         </is>
       </c>
       <c r="C22" s="50" t="n"/>
-      <c r="D22" s="56">
-        <f t="array" ref="D22">_xlfn.SWITCH(E22,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D22" s="56" t="n">
+        <v>3</v>
       </c>
       <c r="E22" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F22" s="9" t="n"/>
@@ -1592,7 +1644,7 @@
       </c>
       <c r="J22" s="23" t="inlineStr">
         <is>
-          <t>Weaker value proposition</t>
+          <t>Very clear value prop: regulatory compliance + patient safety + cycle outcomes</t>
         </is>
       </c>
     </row>
@@ -1603,13 +1655,12 @@
         </is>
       </c>
       <c r="C23" s="51" t="n"/>
-      <c r="D23" s="57">
-        <f t="array" ref="D23">_xlfn.SWITCH(E23,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D23" s="57" t="n">
+        <v>3</v>
       </c>
       <c r="E23" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F23" s="21" t="n"/>
@@ -1630,7 +1681,7 @@
       </c>
       <c r="J23" s="24" t="inlineStr">
         <is>
-          <t>Can be replaced w/effort</t>
+          <t>Extremely high switching costs — embryology data, SART historicals, lab integrations; replatform ~once a decade</t>
         </is>
       </c>
     </row>
@@ -1659,9 +1710,8 @@
         </is>
       </c>
       <c r="C25" s="50" t="n"/>
-      <c r="D25" s="56">
-        <f t="array" ref="D25">_xlfn.SWITCH(E25,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D25" s="56" t="n">
+        <v>3</v>
       </c>
       <c r="E25" s="48" t="inlineStr">
         <is>
@@ -1686,7 +1736,7 @@
       </c>
       <c r="J25" s="23" t="inlineStr">
         <is>
-          <t>High visibility</t>
+          <t>Tech adoption visible — cloud migration + AI lab tools well-telegraphed</t>
         </is>
       </c>
     </row>
@@ -1697,9 +1747,8 @@
         </is>
       </c>
       <c r="C26" s="50" t="n"/>
-      <c r="D26" s="56">
-        <f t="array" ref="D26">_xlfn.SWITCH(E26,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D26" s="56" t="n">
+        <v>2</v>
       </c>
       <c r="E26" s="48" t="inlineStr">
         <is>
@@ -1724,7 +1773,7 @@
       </c>
       <c r="J26" s="23" t="inlineStr">
         <is>
-          <t>Some risk and frequency</t>
+          <t>FDA, SART reporting, HIPAA; state-level IVF regs evolving post-Dobbs (moderate risk)</t>
         </is>
       </c>
     </row>
@@ -1735,13 +1784,12 @@
         </is>
       </c>
       <c r="C27" s="50" t="n"/>
-      <c r="D27" s="56">
-        <f t="array" ref="D27">_xlfn.SWITCH(E27,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D27" s="56" t="n">
+        <v>1</v>
       </c>
       <c r="E27" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F27" s="9" t="n"/>
@@ -1762,7 +1810,7 @@
       </c>
       <c r="J27" s="23" t="inlineStr">
         <is>
-          <t>Some liability risks</t>
+          <t>High liability — embryo mix-ups, genetic errors = catastrophic; software is in the chain</t>
         </is>
       </c>
     </row>
@@ -1773,9 +1821,8 @@
         </is>
       </c>
       <c r="C28" s="50" t="n"/>
-      <c r="D28" s="56">
-        <f t="array" ref="D28">_xlfn.SWITCH(E28,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D28" s="56" t="n">
+        <v>3</v>
       </c>
       <c r="E28" s="48" t="inlineStr">
         <is>
@@ -1800,7 +1847,7 @@
       </c>
       <c r="J28" s="23" t="inlineStr">
         <is>
-          <t>Low cyclicality</t>
+          <t>Low cyclicality — family building demand resilient; employer benefits growing</t>
         </is>
       </c>
     </row>
@@ -1811,9 +1858,8 @@
         </is>
       </c>
       <c r="C29" s="51" t="n"/>
-      <c r="D29" s="57">
-        <f t="array" ref="D29">_xlfn.SWITCH(E29,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D29" s="57" t="n">
+        <v>2</v>
       </c>
       <c r="E29" s="48" t="inlineStr">
         <is>
@@ -1838,7 +1884,7 @@
       </c>
       <c r="J29" s="24" t="inlineStr">
         <is>
-          <t>Some resiliency to trends</t>
+          <t>Vertical integration by benefits platforms (Progyny/Maven/Kindbody) is a structural threat</t>
         </is>
       </c>
     </row>
@@ -1867,13 +1913,12 @@
         </is>
       </c>
       <c r="C31" s="50" t="n"/>
-      <c r="D31" s="56">
-        <f t="array" ref="D31">_xlfn.SWITCH(E31,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D31" s="56" t="n">
+        <v>2</v>
       </c>
       <c r="E31" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="F31" s="9" t="n"/>
@@ -1894,7 +1939,7 @@
       </c>
       <c r="J31" s="23" t="inlineStr">
         <is>
-          <t>No VC-backed companies (only PE-owned)</t>
+          <t>VC-backed entrants present: Alife (AI), Embie, TMRW Life Sciences (cryo)</t>
         </is>
       </c>
     </row>
@@ -1905,9 +1950,8 @@
         </is>
       </c>
       <c r="C32" s="50" t="n"/>
-      <c r="D32" s="56">
-        <f t="array" ref="D32">_xlfn.SWITCH(E32,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D32" s="56" t="n">
+        <v>1</v>
       </c>
       <c r="E32" s="48" t="inlineStr">
         <is>
@@ -1932,7 +1976,7 @@
       </c>
       <c r="J32" s="23" t="inlineStr">
         <is>
-          <t>High competition</t>
+          <t>High competition concentrated among top 2-3; replatform wins are binary</t>
         </is>
       </c>
     </row>
@@ -1943,13 +1987,12 @@
         </is>
       </c>
       <c r="C33" s="50" t="n"/>
-      <c r="D33" s="56">
-        <f t="array" ref="D33">_xlfn.SWITCH(E33,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D33" s="56" t="n">
+        <v>1</v>
       </c>
       <c r="E33" s="48" t="inlineStr">
         <is>
-          <t>+</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F33" s="9" t="n"/>
@@ -1970,7 +2013,7 @@
       </c>
       <c r="J33" s="23" t="inlineStr">
         <is>
-          <t>No new entrants</t>
+          <t>AI-driven new entrants (Alife, Embie) attacking workflow + lab optimization</t>
         </is>
       </c>
     </row>
@@ -2016,13 +2059,12 @@
         </is>
       </c>
       <c r="C35" s="50" t="n"/>
-      <c r="D35" s="56">
-        <f t="array" ref="D35">_xlfn.SWITCH(E35,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D35" s="56" t="n">
+        <v>1</v>
       </c>
       <c r="E35" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F35" s="9" t="n"/>
@@ -2043,7 +2085,7 @@
       </c>
       <c r="J35" s="23" t="inlineStr">
         <is>
-          <t>Some customer power</t>
+          <t>PE-consolidated clinic groups (IVI RMA/KKR, US Fertility/L Catterton, Inception, Kindbody) = concentrated buyer power</t>
         </is>
       </c>
     </row>
@@ -2054,13 +2096,12 @@
         </is>
       </c>
       <c r="C36" s="51" t="n"/>
-      <c r="D36" s="57">
-        <f t="array" ref="D36">_xlfn.SWITCH(E36,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D36" s="57" t="n">
+        <v>1</v>
       </c>
       <c r="E36" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F36" s="21" t="n"/>
@@ -2081,7 +2122,7 @@
       </c>
       <c r="J36" s="24" t="inlineStr">
         <is>
-          <t>Some substitutes</t>
+          <t>Progyny/Maven/Kindbody vertical integration = substitute threat (owned stack for managed clinics)</t>
         </is>
       </c>
     </row>
@@ -2110,9 +2151,8 @@
         </is>
       </c>
       <c r="C38" s="50" t="n"/>
-      <c r="D38" s="56">
-        <f t="array" ref="D38">_xlfn.SWITCH(E38,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D38" s="56" t="n">
+        <v>2</v>
       </c>
       <c r="E38" s="48" t="inlineStr">
         <is>
@@ -2137,7 +2177,7 @@
       </c>
       <c r="J38" s="23" t="inlineStr">
         <is>
-          <t>Moderate complexity</t>
+          <t>Moderate — embryology workflow + regulatory reporting requires domain expertise</t>
         </is>
       </c>
     </row>
@@ -2148,9 +2188,8 @@
         </is>
       </c>
       <c r="C39" s="51" t="n"/>
-      <c r="D39" s="57">
-        <f t="array" ref="D39">_xlfn.SWITCH(E39,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D39" s="57" t="n">
+        <v>2</v>
       </c>
       <c r="E39" s="48" t="inlineStr">
         <is>
@@ -2175,7 +2214,7 @@
       </c>
       <c r="J39" s="24" t="inlineStr">
         <is>
-          <t>Some actionable levers</t>
+          <t>Some levers: cloud migration, AI lab tools, patient engagement expansion</t>
         </is>
       </c>
     </row>
@@ -2204,13 +2243,12 @@
         </is>
       </c>
       <c r="C41" s="50" t="n"/>
-      <c r="D41" s="56">
-        <f t="array" ref="D41">_xlfn.SWITCH(E41,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D41" s="56" t="n">
+        <v>3</v>
       </c>
       <c r="E41" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F41" s="9" t="n"/>
@@ -2231,7 +2269,7 @@
       </c>
       <c r="J41" s="23" t="inlineStr">
         <is>
-          <t>Neutral impact</t>
+          <t>Net positive — enables family building, improves cycle outcomes &amp; patient safety</t>
         </is>
       </c>
     </row>
@@ -2242,13 +2280,12 @@
         </is>
       </c>
       <c r="C42" s="52" t="n"/>
-      <c r="D42" s="56">
-        <f t="array" ref="D42">_xlfn.SWITCH(E42,"+",3,"+/-",2,"-",1)</f>
-        <v/>
+      <c r="D42" s="56" t="n">
+        <v>3</v>
       </c>
       <c r="E42" s="48" t="inlineStr">
         <is>
-          <t>+/-</t>
+          <t>+</t>
         </is>
       </c>
       <c r="F42" s="13" t="n"/>
@@ -2269,7 +2306,7 @@
       </c>
       <c r="J42" s="25" t="inlineStr">
         <is>
-          <t>Neutral externalities</t>
+          <t>Positive externalities — embryology safety, genetic screening accuracy</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2322,7 @@
       </c>
       <c r="D43" s="18" t="inlineStr">
         <is>
-          <t>Commentary: N/A</t>
+          <t>Commentary: Strong business quality (recurring SaaS, mission critical, high switching costs) but FAILS Initial Screen on Growth TAM (~$200-400M vs $500M floor). Winner-take-most + benefits-platform vertical integration (Progyny/Maven/Kindbody) cap upside. Excellent fundamentals, insufficient scale for G&amp;B.</t>
         </is>
       </c>
       <c r="E43" s="18" t="n"/>
